--- a/data-collection/netty.xlsx
+++ b/data-collection/netty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politechnikawroclawska-my.sharepoint.com/personal/260364_student_pwr_edu_pl/Documents/Semestr10-3mgr/dyplomowe/ai/data-collection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542F1749-4325-468A-9E78-56DD3BDFE396}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_F25DC773A252ABDACC1048A6391B61545ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{989589ED-DEC7-4137-92D5-1D45E493A977}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="-11640" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="353">
   <si>
     <t>Wersja</t>
   </si>
@@ -646,12 +646,486 @@
   </si>
   <si>
     <t>4.0.0</t>
+  </si>
+  <si>
+    <t>Dec 22, 2013</t>
+  </si>
+  <si>
+    <t>Jan 14, 2025</t>
+  </si>
+  <si>
+    <t>Dec 17, 2024</t>
+  </si>
+  <si>
+    <t>Nov 12, 2024</t>
+  </si>
+  <si>
+    <t>Oct 01, 2024</t>
+  </si>
+  <si>
+    <t>Sep 04, 2024</t>
+  </si>
+  <si>
+    <t>Jul 19, 2024</t>
+  </si>
+  <si>
+    <t>Jun 11, 2024</t>
+  </si>
+  <si>
+    <t>May 22, 2024</t>
+  </si>
+  <si>
+    <t>Apr 15, 2024</t>
+  </si>
+  <si>
+    <t>Mar 21, 2024</t>
+  </si>
+  <si>
+    <t>Feb 13, 2024</t>
+  </si>
+  <si>
+    <t>Jan 19, 2024</t>
+  </si>
+  <si>
+    <t>Jan 16, 2024</t>
+  </si>
+  <si>
+    <t>Dec 15, 2023</t>
+  </si>
+  <si>
+    <t>Dec 13, 2023</t>
+  </si>
+  <si>
+    <t>Nov 09, 2023</t>
+  </si>
+  <si>
+    <t>Oct 10, 2023</t>
+  </si>
+  <si>
+    <t>Sep 28, 2023</t>
+  </si>
+  <si>
+    <t>Sep 21, 2023</t>
+  </si>
+  <si>
+    <t>Aug 23, 2023</t>
+  </si>
+  <si>
+    <t>Jul 27, 2023</t>
+  </si>
+  <si>
+    <t>Jul 20, 2023</t>
+  </si>
+  <si>
+    <t>Jun 20, 2023</t>
+  </si>
+  <si>
+    <t>May 25, 2023</t>
+  </si>
+  <si>
+    <t>Apr 25, 2023</t>
+  </si>
+  <si>
+    <t>Apr 03, 2023</t>
+  </si>
+  <si>
+    <t>Mar 14, 2023</t>
+  </si>
+  <si>
+    <t>Feb 13, 2023</t>
+  </si>
+  <si>
+    <t>Feb 12, 2023</t>
+  </si>
+  <si>
+    <t>Jan 12, 2023</t>
+  </si>
+  <si>
+    <t>Dec 12, 2022</t>
+  </si>
+  <si>
+    <t>Nov 09, 2022</t>
+  </si>
+  <si>
+    <t>Oct 12, 2022</t>
+  </si>
+  <si>
+    <t>Oct 11, 2022</t>
+  </si>
+  <si>
+    <t>Sep 13, 2022</t>
+  </si>
+  <si>
+    <t>Sep 08, 2022</t>
+  </si>
+  <si>
+    <t>Aug 26, 2022</t>
+  </si>
+  <si>
+    <t>Jul 11, 2022</t>
+  </si>
+  <si>
+    <t>Jun 14, 2022</t>
+  </si>
+  <si>
+    <t>May 06, 2022</t>
+  </si>
+  <si>
+    <t>Apr 12, 2022</t>
+  </si>
+  <si>
+    <t>Mar 10, 2022</t>
+  </si>
+  <si>
+    <t>Feb 08, 2022</t>
+  </si>
+  <si>
+    <t>Jan 12, 2022</t>
+  </si>
+  <si>
+    <t>Dec 13, 2021</t>
+  </si>
+  <si>
+    <t>Dec 09, 2021</t>
+  </si>
+  <si>
+    <t>Nov 03, 2021</t>
+  </si>
+  <si>
+    <t>Oct 11, 2021</t>
+  </si>
+  <si>
+    <t>Sep 09, 2021</t>
+  </si>
+  <si>
+    <t>Aug 16, 2021</t>
+  </si>
+  <si>
+    <t>Jul 16, 2021</t>
+  </si>
+  <si>
+    <t>May 19, 2021</t>
+  </si>
+  <si>
+    <t>May 17, 2021</t>
+  </si>
+  <si>
+    <t>Apr 01, 2021</t>
+  </si>
+  <si>
+    <t>Mar 30, 2021</t>
+  </si>
+  <si>
+    <t>Mar 09, 2021</t>
+  </si>
+  <si>
+    <t>Feb 08, 2021</t>
+  </si>
+  <si>
+    <t>Jan 13, 2021</t>
+  </si>
+  <si>
+    <t>Jan 12, 2021</t>
+  </si>
+  <si>
+    <t>Dec 17, 2020</t>
+  </si>
+  <si>
+    <t>Dec 08, 2020</t>
+  </si>
+  <si>
+    <t>Nov 11, 2020</t>
+  </si>
+  <si>
+    <t>Oct 13, 2020</t>
+  </si>
+  <si>
+    <t>Sep 08, 2020</t>
+  </si>
+  <si>
+    <t>Jul 09, 2020</t>
+  </si>
+  <si>
+    <t>May 13, 2020</t>
+  </si>
+  <si>
+    <t>Apr 22, 2020</t>
+  </si>
+  <si>
+    <t>Mar 17, 2020</t>
+  </si>
+  <si>
+    <t>Mar 09, 2020</t>
+  </si>
+  <si>
+    <t>Feb 28, 2020</t>
+  </si>
+  <si>
+    <t>Jan 13, 2020</t>
+  </si>
+  <si>
+    <t>Dec 18, 2019</t>
+  </si>
+  <si>
+    <t>Oct 24, 2019</t>
+  </si>
+  <si>
+    <t>Sep 27, 2019</t>
+  </si>
+  <si>
+    <t>Sep 12, 2019</t>
+  </si>
+  <si>
+    <t>Aug 13, 2019</t>
+  </si>
+  <si>
+    <t>Jul 24, 2019</t>
+  </si>
+  <si>
+    <t>Jun 28, 2019</t>
+  </si>
+  <si>
+    <t>Apr 30, 2019</t>
+  </si>
+  <si>
+    <t>Apr 17, 2019</t>
+  </si>
+  <si>
+    <t>Mar 08, 2019</t>
+  </si>
+  <si>
+    <t>Jan 21, 2019</t>
+  </si>
+  <si>
+    <t>Nov 29, 2018</t>
+  </si>
+  <si>
+    <t>Oct 30, 2018</t>
+  </si>
+  <si>
+    <t>Sep 28, 2018</t>
+  </si>
+  <si>
+    <t>Aug 24, 2018</t>
+  </si>
+  <si>
+    <t>Jul 27, 2018</t>
+  </si>
+  <si>
+    <t>Jul 11, 2018</t>
+  </si>
+  <si>
+    <t>Jul 10, 2018</t>
+  </si>
+  <si>
+    <t>May 14, 2018</t>
+  </si>
+  <si>
+    <t>Apr 19, 2018</t>
+  </si>
+  <si>
+    <t>Apr 04, 2018</t>
+  </si>
+  <si>
+    <t>Feb 21, 2018</t>
+  </si>
+  <si>
+    <t>Feb 05, 2018</t>
+  </si>
+  <si>
+    <t>Jan 21, 2018</t>
+  </si>
+  <si>
+    <t>Dec 15, 2017</t>
+  </si>
+  <si>
+    <t>Dec 08, 2017</t>
+  </si>
+  <si>
+    <t>Nov 08, 2017</t>
+  </si>
+  <si>
+    <t>Sep 25, 2017</t>
+  </si>
+  <si>
+    <t>Aug 24, 2017</t>
+  </si>
+  <si>
+    <t>Aug 02, 2017</t>
+  </si>
+  <si>
+    <t>Jul 06, 2017</t>
+  </si>
+  <si>
+    <t>Jun 08, 2017</t>
+  </si>
+  <si>
+    <t>May 11, 2017</t>
+  </si>
+  <si>
+    <t>Apr 29, 2017</t>
+  </si>
+  <si>
+    <t>Mar 10, 2017</t>
+  </si>
+  <si>
+    <t>Jan 30, 2017</t>
+  </si>
+  <si>
+    <t>Jan 12, 2017</t>
+  </si>
+  <si>
+    <t>Oct 14, 2016</t>
+  </si>
+  <si>
+    <t>Aug 29, 2016</t>
+  </si>
+  <si>
+    <t>Jul 27, 2016</t>
+  </si>
+  <si>
+    <t>Jul 15, 2016</t>
+  </si>
+  <si>
+    <t>Jul 01, 2016</t>
+  </si>
+  <si>
+    <t>Jun 07, 2016</t>
+  </si>
+  <si>
+    <t>May 25, 2016</t>
+  </si>
+  <si>
+    <t>Mar 21, 2016</t>
+  </si>
+  <si>
+    <t>Sep 02, 2015</t>
+  </si>
+  <si>
+    <t>May 07, 2015</t>
+  </si>
+  <si>
+    <t>Aug 15, 2014</t>
+  </si>
+  <si>
+    <t>Nov 09, 2017</t>
+  </si>
+  <si>
+    <t>Sep 21, 2017</t>
+  </si>
+  <si>
+    <t>Jun 09, 2017</t>
+  </si>
+  <si>
+    <t>Apr 04, 2016</t>
+  </si>
+  <si>
+    <t>Jan 29, 2016</t>
+  </si>
+  <si>
+    <t>Nov 03, 2015</t>
+  </si>
+  <si>
+    <t>Sep 30, 2015</t>
+  </si>
+  <si>
+    <t>Jul 24, 2015</t>
+  </si>
+  <si>
+    <t>Jun 23, 2015</t>
+  </si>
+  <si>
+    <t>Apr 02, 2015</t>
+  </si>
+  <si>
+    <t>Mar 02, 2015</t>
+  </si>
+  <si>
+    <t>Dec 31, 2014</t>
+  </si>
+  <si>
+    <t>Oct 29, 2014</t>
+  </si>
+  <si>
+    <t>Aug 14, 2014</t>
+  </si>
+  <si>
+    <t>Jul 01, 2014</t>
+  </si>
+  <si>
+    <t>Jun 12, 2014</t>
+  </si>
+  <si>
+    <t>Apr 30, 2014</t>
+  </si>
+  <si>
+    <t>Apr 01, 2014</t>
+  </si>
+  <si>
+    <t>Feb 24, 2014</t>
+  </si>
+  <si>
+    <t>Feb 20, 2014</t>
+  </si>
+  <si>
+    <t>Jan 21, 2014</t>
+  </si>
+  <si>
+    <t>Nov 28, 2013</t>
+  </si>
+  <si>
+    <t>Nov 07, 2013</t>
+  </si>
+  <si>
+    <t>Oct 21, 2013</t>
+  </si>
+  <si>
+    <t>Oct 03, 2013</t>
+  </si>
+  <si>
+    <t>Sep 06, 2013</t>
+  </si>
+  <si>
+    <t>Aug 26, 2013</t>
+  </si>
+  <si>
+    <t>Aug 08, 2013</t>
+  </si>
+  <si>
+    <t>Aug 01, 2013</t>
+  </si>
+  <si>
+    <t>Jul 31, 2013</t>
+  </si>
+  <si>
+    <t>Jul 23, 2013</t>
+  </si>
+  <si>
+    <t>Jul 18, 2013</t>
+  </si>
+  <si>
+    <t>Jul 17, 2013</t>
+  </si>
+  <si>
+    <t>Jul 16, 2013</t>
+  </si>
+  <si>
+    <t>Jul 15, 2013</t>
+  </si>
+  <si>
+    <t>4.0.x</t>
+  </si>
+  <si>
+    <t>Data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -681,8 +1155,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -698,6 +1174,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -963,13 +1443,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1483"/>
+  <dimension ref="A1:N1483"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -983,7 +1465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1000,12 +1482,15 @@
         <f t="array" ref="H2:H177">_xlfn._xlws.FILTER(A:A, LEN(A:A)&gt;0)</f>
         <v>Wersja</v>
       </c>
-      <c r="I2" t="str" cm="1">
-        <f t="array" ref="I2:I177">_xlfn._xlws.FILTER(D:D, LEN(D:D) &gt; 0)</f>
+      <c r="I2" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J177">_xlfn._xlws.FILTER(D:D, LEN(D:D) &gt; 0)</f>
         <v>Mediana</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -1015,11 +1500,14 @@
       <c r="H3" t="str">
         <v>4.1.117</v>
       </c>
-      <c r="I3">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J3">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1035,11 +1523,14 @@
       <c r="H4" t="str">
         <v>4.1.116</v>
       </c>
-      <c r="I4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -1049,11 +1540,14 @@
       <c r="H5" t="str">
         <v>4.1.115</v>
       </c>
-      <c r="I5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1063,11 +1557,14 @@
       <c r="H6" t="str">
         <v>4.1.114</v>
       </c>
-      <c r="I6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I6" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1083,11 +1580,14 @@
       <c r="H7" t="str">
         <v>4.1.113</v>
       </c>
-      <c r="I7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -1097,11 +1597,14 @@
       <c r="H8" t="str">
         <v>4.1.112</v>
       </c>
-      <c r="I8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I8" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -1111,11 +1614,14 @@
       <c r="H9" t="str">
         <v>4.1.111</v>
       </c>
-      <c r="I9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1131,11 +1637,14 @@
       <c r="H10" t="str">
         <v>4.1.110</v>
       </c>
-      <c r="I10">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J10">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>6</v>
       </c>
@@ -1145,11 +1654,14 @@
       <c r="H11" t="str">
         <v>4.1.109</v>
       </c>
-      <c r="I11">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J11">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -1159,11 +1671,14 @@
       <c r="H12" t="str">
         <v>4.1.108</v>
       </c>
-      <c r="I12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I12" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="J12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>11</v>
       </c>
@@ -1173,11 +1688,14 @@
       <c r="H13" t="str">
         <v>4.1.107</v>
       </c>
-      <c r="I13">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J13">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1193,11 +1711,14 @@
       <c r="H14" t="str">
         <v>4.1.106</v>
       </c>
-      <c r="I14">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J14">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>6</v>
       </c>
@@ -1207,11 +1728,14 @@
       <c r="H15" t="str">
         <v>4.1.105</v>
       </c>
-      <c r="I15">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J15">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>8</v>
       </c>
@@ -1221,11 +1745,14 @@
       <c r="H16" t="str">
         <v>4.1.104</v>
       </c>
-      <c r="I16">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J16">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>11</v>
       </c>
@@ -1235,11 +1762,14 @@
       <c r="H17" t="str">
         <v>4.1.103</v>
       </c>
-      <c r="I17">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J17">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1255,11 +1785,14 @@
       <c r="H18" t="str">
         <v>4.1.102</v>
       </c>
-      <c r="I18">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J18">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>6</v>
       </c>
@@ -1269,11 +1802,14 @@
       <c r="H19" t="str">
         <v>4.1.101</v>
       </c>
-      <c r="I19">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I19" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J19">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>8</v>
       </c>
@@ -1283,11 +1819,14 @@
       <c r="H20" t="str">
         <v>4.1.100</v>
       </c>
-      <c r="I20">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I20" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J20">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>11</v>
       </c>
@@ -1297,11 +1836,14 @@
       <c r="H21" t="str">
         <v>4.1.99</v>
       </c>
-      <c r="I21">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I21" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J21">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1317,11 +1859,14 @@
       <c r="H22" t="str">
         <v>4.1.98</v>
       </c>
-      <c r="I22">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I22" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J22">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>6</v>
       </c>
@@ -1331,11 +1876,14 @@
       <c r="H23" t="str">
         <v>4.1.97</v>
       </c>
-      <c r="I23">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I23" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J23">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -1345,11 +1893,14 @@
       <c r="H24" t="str">
         <v>4.1.96</v>
       </c>
-      <c r="I24">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I24" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J24">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>11</v>
       </c>
@@ -1359,11 +1910,14 @@
       <c r="H25" t="str">
         <v>4.1.95</v>
       </c>
-      <c r="I25">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I25" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J25">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -1379,11 +1933,14 @@
       <c r="H26" t="str">
         <v>4.1.94</v>
       </c>
-      <c r="I26">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I26" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="J26">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>6</v>
       </c>
@@ -1393,11 +1950,14 @@
       <c r="H27" t="str">
         <v>4.1.93</v>
       </c>
-      <c r="I27">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I27" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J27">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>8</v>
       </c>
@@ -1407,11 +1967,14 @@
       <c r="H28" t="str">
         <v>4.1.92</v>
       </c>
-      <c r="I28">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J28">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>11</v>
       </c>
@@ -1421,11 +1984,14 @@
       <c r="H29" t="str">
         <v>4.1.91</v>
       </c>
-      <c r="I29">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I29" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J29">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1441,11 +2007,14 @@
       <c r="H30" t="str">
         <v>4.1.90</v>
       </c>
-      <c r="I30">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I30" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J30">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>6</v>
       </c>
@@ -1455,11 +2024,14 @@
       <c r="H31" t="str">
         <v>4.1.89</v>
       </c>
-      <c r="I31">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I31" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J31">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>8</v>
       </c>
@@ -1469,11 +2041,14 @@
       <c r="H32" t="str">
         <v>4.1.88</v>
       </c>
-      <c r="I32">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J32">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>11</v>
       </c>
@@ -1483,11 +2058,14 @@
       <c r="H33" t="str">
         <v>4.1.87</v>
       </c>
-      <c r="I33">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I33" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J33">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -1503,11 +2081,14 @@
       <c r="H34" t="str">
         <v>4.1.86</v>
       </c>
-      <c r="I34">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I34" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J34">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>6</v>
       </c>
@@ -1517,11 +2098,14 @@
       <c r="H35" t="str">
         <v>4.1.85</v>
       </c>
-      <c r="I35">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I35" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>8</v>
       </c>
@@ -1531,11 +2115,14 @@
       <c r="H36" t="str">
         <v>4.1.84</v>
       </c>
-      <c r="I36">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I36" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J36">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>11</v>
       </c>
@@ -1545,11 +2132,14 @@
       <c r="H37" t="str">
         <v>4.1.83</v>
       </c>
-      <c r="I37">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I37" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J37">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -1565,11 +2155,14 @@
       <c r="H38" t="str">
         <v>4.1.82</v>
       </c>
-      <c r="I38">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I38" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J38">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>5</v>
       </c>
@@ -1579,11 +2172,14 @@
       <c r="H39" t="str">
         <v>4.1.81</v>
       </c>
-      <c r="I39">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I39" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J39">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>6</v>
       </c>
@@ -1593,11 +2189,14 @@
       <c r="H40" t="str">
         <v>4.1.80</v>
       </c>
-      <c r="I40">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I40" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J40">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>8</v>
       </c>
@@ -1607,11 +2206,14 @@
       <c r="H41" t="str">
         <v>4.1.79</v>
       </c>
-      <c r="I41">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I41" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="J41">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>11</v>
       </c>
@@ -1621,11 +2223,14 @@
       <c r="H42" t="str">
         <v>4.1.78</v>
       </c>
-      <c r="I42">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I42" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J42">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -1641,11 +2246,14 @@
       <c r="H43" t="str">
         <v>4.1.77</v>
       </c>
-      <c r="I43">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I43" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="J43">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>5</v>
       </c>
@@ -1655,11 +2263,14 @@
       <c r="H44" t="str">
         <v>4.1.76</v>
       </c>
-      <c r="I44">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I44" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J44">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>6</v>
       </c>
@@ -1669,11 +2280,14 @@
       <c r="H45" t="str">
         <v>4.1.75</v>
       </c>
-      <c r="I45">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I45" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>8</v>
       </c>
@@ -1683,11 +2297,14 @@
       <c r="H46" t="str">
         <v>4.1.74</v>
       </c>
-      <c r="I46">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I46" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J46">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>11</v>
       </c>
@@ -1697,11 +2314,14 @@
       <c r="H47" t="str">
         <v>4.1.73</v>
       </c>
-      <c r="I47">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I47" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J47">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -1717,11 +2337,14 @@
       <c r="H48" t="str">
         <v>4.1.72</v>
       </c>
-      <c r="I48">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I48" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J48">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>5</v>
       </c>
@@ -1731,11 +2354,14 @@
       <c r="H49" t="str">
         <v>4.1.71</v>
       </c>
-      <c r="I49">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I49" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J49">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>6</v>
       </c>
@@ -1745,11 +2371,14 @@
       <c r="H50" t="str">
         <v>4.1.70</v>
       </c>
-      <c r="I50">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I50" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J50">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>8</v>
       </c>
@@ -1759,11 +2388,14 @@
       <c r="H51" t="str">
         <v>4.1.69</v>
       </c>
-      <c r="I51">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I51" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J51">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>11</v>
       </c>
@@ -1773,11 +2405,14 @@
       <c r="H52" t="str">
         <v>4.1.68</v>
       </c>
-      <c r="I52">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I52" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J52">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -1793,11 +2428,14 @@
       <c r="H53" t="str">
         <v>4.1.67</v>
       </c>
-      <c r="I53">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I53" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="J53">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>5</v>
       </c>
@@ -1807,11 +2445,14 @@
       <c r="H54" t="str">
         <v>4.1.66</v>
       </c>
-      <c r="I54">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I54" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J54">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>6</v>
       </c>
@@ -1821,11 +2462,14 @@
       <c r="H55" t="str">
         <v>4.1.65</v>
       </c>
-      <c r="I55">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I55" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J55">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>8</v>
       </c>
@@ -1835,11 +2479,14 @@
       <c r="H56" t="str">
         <v>4.1.64</v>
       </c>
-      <c r="I56">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I56" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J56">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>11</v>
       </c>
@@ -1849,11 +2496,14 @@
       <c r="H57" t="str">
         <v>4.1.63</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J57">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -1869,11 +2519,14 @@
       <c r="H58" t="str">
         <v>4.1.62</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J58">
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>5</v>
       </c>
@@ -1883,11 +2536,14 @@
       <c r="H59" t="str">
         <v>4.1.61</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J59">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>6</v>
       </c>
@@ -1897,11 +2553,14 @@
       <c r="H60" t="str">
         <v>4.1.60</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J60">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>8</v>
       </c>
@@ -1911,11 +2570,14 @@
       <c r="H61" t="str">
         <v>4.1.59</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J61">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>11</v>
       </c>
@@ -1925,11 +2587,14 @@
       <c r="H62" t="str">
         <v>4.1.58</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J62">
         <v>6.2</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -1945,11 +2610,14 @@
       <c r="H63" t="str">
         <v>4.1.57</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J63">
         <v>6.2</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>5</v>
       </c>
@@ -1959,11 +2627,14 @@
       <c r="H64" t="str">
         <v>4.1.56</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="J64">
         <v>6.2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>6</v>
       </c>
@@ -1973,11 +2644,14 @@
       <c r="H65" t="str">
         <v>4.1.55</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J65">
         <v>6.2</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>8</v>
       </c>
@@ -1987,11 +2661,14 @@
       <c r="H66" t="str">
         <v>4.1.54</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J66">
         <v>6.2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>11</v>
       </c>
@@ -2001,11 +2678,14 @@
       <c r="H67" t="str">
         <v>4.1.53</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J67">
         <v>6.2</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -2021,11 +2701,14 @@
       <c r="H68" t="str">
         <v>4.1.52</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J68">
         <v>6.2</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>5</v>
       </c>
@@ -2035,11 +2718,14 @@
       <c r="H69" t="str">
         <v>4.1.51</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J69">
         <v>6.2</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>6</v>
       </c>
@@ -2049,11 +2735,14 @@
       <c r="H70" t="str">
         <v>4.1.50</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J70">
         <v>6.2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>8</v>
       </c>
@@ -2063,11 +2752,14 @@
       <c r="H71" t="str">
         <v>4.1.49</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J71">
         <v>6.2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>11</v>
       </c>
@@ -2077,11 +2769,14 @@
       <c r="H72" t="str">
         <v>4.1.48</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="J72">
         <v>6.2</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>26</v>
       </c>
@@ -2097,11 +2792,14 @@
       <c r="H73" t="str">
         <v>4.1.47</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J73">
         <v>6.2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>5</v>
       </c>
@@ -2111,11 +2809,14 @@
       <c r="H74" t="str">
         <v>4.1.46</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J74">
         <v>6.2</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>6</v>
       </c>
@@ -2125,11 +2826,14 @@
       <c r="H75" t="str">
         <v>4.1.45</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J75">
         <v>6.35</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>8</v>
       </c>
@@ -2139,11 +2843,14 @@
       <c r="H76" t="str">
         <v>4.1.44</v>
       </c>
-      <c r="I76">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I76" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="J76">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>11</v>
       </c>
@@ -2153,11 +2860,14 @@
       <c r="H77" t="str">
         <v>4.1.43</v>
       </c>
-      <c r="I77">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I77" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J77">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>27</v>
       </c>
@@ -2173,11 +2883,14 @@
       <c r="H78" t="str">
         <v>4.1.42</v>
       </c>
-      <c r="I78">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I78" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J78">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>5</v>
       </c>
@@ -2187,11 +2900,14 @@
       <c r="H79" t="str">
         <v>4.1.41</v>
       </c>
-      <c r="I79">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I79" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J79">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>6</v>
       </c>
@@ -2201,11 +2917,14 @@
       <c r="H80" t="str">
         <v>4.1.40</v>
       </c>
-      <c r="I80">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I80" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J80">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>8</v>
       </c>
@@ -2215,11 +2934,14 @@
       <c r="H81" t="str">
         <v>4.1.39</v>
       </c>
-      <c r="I81">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I81" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J81">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>11</v>
       </c>
@@ -2229,11 +2951,14 @@
       <c r="H82" t="str">
         <v>4.1.38</v>
       </c>
-      <c r="I82">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I82" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J82">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -2249,11 +2974,14 @@
       <c r="H83" t="str">
         <v>4.1.37</v>
       </c>
-      <c r="I83">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I83" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J83">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>5</v>
       </c>
@@ -2263,11 +2991,14 @@
       <c r="H84" t="str">
         <v>4.1.36</v>
       </c>
-      <c r="I84">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I84" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="J84">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>6</v>
       </c>
@@ -2277,11 +3008,14 @@
       <c r="H85" t="str">
         <v>4.1.35</v>
       </c>
-      <c r="I85">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I85" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J85">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>8</v>
       </c>
@@ -2291,11 +3025,14 @@
       <c r="H86" t="str">
         <v>4.1.34</v>
       </c>
-      <c r="I86">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I86" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J86">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>11</v>
       </c>
@@ -2305,11 +3042,14 @@
       <c r="H87" t="str">
         <v>4.1.33</v>
       </c>
-      <c r="I87">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I87" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="J87">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -2325,11 +3065,14 @@
       <c r="H88" t="str">
         <v>4.1.32</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J88">
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>5</v>
       </c>
@@ -2339,11 +3082,14 @@
       <c r="H89" t="str">
         <v>4.1.31</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J89">
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>6</v>
       </c>
@@ -2353,11 +3099,14 @@
       <c r="H90" t="str">
         <v>4.1.30</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="J90">
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>8</v>
       </c>
@@ -2367,11 +3116,14 @@
       <c r="H91" t="str">
         <v>4.1.29</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J91">
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>11</v>
       </c>
@@ -2381,11 +3133,14 @@
       <c r="H92" t="str">
         <v>4.1.28</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J92">
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -2401,11 +3156,14 @@
       <c r="H93" t="str">
         <v>4.1.27</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J93">
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>5</v>
       </c>
@@ -2415,11 +3173,14 @@
       <c r="H94" t="str">
         <v>4.1.26</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="J94">
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>6</v>
       </c>
@@ -2429,11 +3190,14 @@
       <c r="H95" t="str">
         <v>4.1.25</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J95">
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>8</v>
       </c>
@@ -2443,11 +3207,14 @@
       <c r="H96" t="str">
         <v>4.1.24</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="J96">
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>11</v>
       </c>
@@ -2457,11 +3224,14 @@
       <c r="H97" t="str">
         <v>4.1.23</v>
       </c>
-      <c r="I97">
+      <c r="I97" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J97">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>31</v>
       </c>
@@ -2477,11 +3247,14 @@
       <c r="H98" t="str">
         <v>4.1.22</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J98">
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>5</v>
       </c>
@@ -2491,11 +3264,14 @@
       <c r="H99" t="str">
         <v>4.1.21</v>
       </c>
-      <c r="I99">
+      <c r="I99" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J99">
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>6</v>
       </c>
@@ -2505,11 +3281,14 @@
       <c r="H100" t="str">
         <v>4.1.20</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="J100">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>8</v>
       </c>
@@ -2519,11 +3298,14 @@
       <c r="H101" t="str">
         <v>4.1.19</v>
       </c>
-      <c r="I101">
+      <c r="I101" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J101">
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>11</v>
       </c>
@@ -2533,11 +3315,14 @@
       <c r="H102" t="str">
         <v>4.1.18</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="J102">
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -2553,11 +3338,14 @@
       <c r="H103" t="str">
         <v>4.1.17</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J103">
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>5</v>
       </c>
@@ -2567,11 +3355,14 @@
       <c r="H104" t="str">
         <v>4.1.16</v>
       </c>
-      <c r="I104">
+      <c r="I104" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="J104">
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>6</v>
       </c>
@@ -2581,11 +3372,14 @@
       <c r="H105" t="str">
         <v>4.1.15</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="J105">
         <v>6.2</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>8</v>
       </c>
@@ -2595,11 +3389,14 @@
       <c r="H106" t="str">
         <v>4.1.14</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J106">
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>11</v>
       </c>
@@ -2609,11 +3406,14 @@
       <c r="H107" t="str">
         <v>4.1.13</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="J107">
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -2629,11 +3429,14 @@
       <c r="H108" t="str">
         <v>4.1.12</v>
       </c>
-      <c r="I108">
+      <c r="I108" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J108">
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>5</v>
       </c>
@@ -2643,11 +3446,14 @@
       <c r="H109" t="str">
         <v>4.1.11</v>
       </c>
-      <c r="I109">
+      <c r="I109" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="J109">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>6</v>
       </c>
@@ -2657,11 +3463,14 @@
       <c r="H110" t="str">
         <v>4.1.10</v>
       </c>
-      <c r="I110">
+      <c r="I110" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J110">
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>8</v>
       </c>
@@ -2671,11 +3480,14 @@
       <c r="H111" t="str">
         <v>4.1.9</v>
       </c>
-      <c r="I111">
+      <c r="I111" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J111">
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>11</v>
       </c>
@@ -2685,11 +3497,14 @@
       <c r="H112" t="str">
         <v>4.1.8</v>
       </c>
-      <c r="I112">
+      <c r="I112" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J112">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>34</v>
       </c>
@@ -2699,11 +3514,14 @@
       <c r="H113" t="str">
         <v>4.1.7</v>
       </c>
-      <c r="I113">
+      <c r="I113" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J113">
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>35</v>
       </c>
@@ -2719,11 +3537,14 @@
       <c r="H114" t="str">
         <v>4.1.6</v>
       </c>
-      <c r="I114">
+      <c r="I114" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J114">
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>5</v>
       </c>
@@ -2733,11 +3554,14 @@
       <c r="H115" t="str">
         <v>4.1.5</v>
       </c>
-      <c r="I115">
+      <c r="I115" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="J115">
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>6</v>
       </c>
@@ -2747,11 +3571,14 @@
       <c r="H116" t="str">
         <v>4.1.4</v>
       </c>
-      <c r="I116">
+      <c r="I116" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="J116">
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>8</v>
       </c>
@@ -2761,11 +3588,14 @@
       <c r="H117" t="str">
         <v>4.1.3</v>
       </c>
-      <c r="I117">
+      <c r="I117" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J117">
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>11</v>
       </c>
@@ -2775,11 +3605,14 @@
       <c r="H118" t="str">
         <v>4.1.2</v>
       </c>
-      <c r="I118">
+      <c r="I118" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J118">
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>34</v>
       </c>
@@ -2789,11 +3622,14 @@
       <c r="H119" t="str">
         <v>4.1.1</v>
       </c>
-      <c r="I119">
+      <c r="I119" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="J119">
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>36</v>
       </c>
@@ -2809,11 +3645,14 @@
       <c r="H120" t="str">
         <v>4.1.0</v>
       </c>
-      <c r="I120">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I120" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J120">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>5</v>
       </c>
@@ -2823,11 +3662,14 @@
       <c r="H121" t="str">
         <v>4.0.56</v>
       </c>
-      <c r="I121">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I121" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="J121">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>6</v>
       </c>
@@ -2837,11 +3679,14 @@
       <c r="H122" t="str">
         <v>4.0.55</v>
       </c>
-      <c r="I122">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J122">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>8</v>
       </c>
@@ -2851,11 +3696,14 @@
       <c r="H123" t="str">
         <v>4.0.54</v>
       </c>
-      <c r="I123">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J123">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>11</v>
       </c>
@@ -2865,11 +3713,14 @@
       <c r="H124" t="str">
         <v>4.0.53</v>
       </c>
-      <c r="I124">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I124" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J124">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>34</v>
       </c>
@@ -2879,11 +3730,14 @@
       <c r="H125" t="str">
         <v>4.0.52</v>
       </c>
-      <c r="I125">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I125" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="J125">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>37</v>
       </c>
@@ -2899,11 +3753,14 @@
       <c r="H126" t="str">
         <v>4.0.51</v>
       </c>
-      <c r="I126">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I126" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J126">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>5</v>
       </c>
@@ -2913,11 +3770,14 @@
       <c r="H127" t="str">
         <v>4.0.50</v>
       </c>
-      <c r="I127">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I127" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J127">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>8</v>
       </c>
@@ -2927,11 +3787,14 @@
       <c r="H128" t="str">
         <v>4.0.49</v>
       </c>
-      <c r="I128">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I128" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J128">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>11</v>
       </c>
@@ -2941,11 +3804,14 @@
       <c r="H129" t="str">
         <v>4.0.48</v>
       </c>
-      <c r="I129">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I129" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J129">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>34</v>
       </c>
@@ -2955,11 +3821,14 @@
       <c r="H130" t="str">
         <v>4.0.47</v>
       </c>
-      <c r="I130">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I130" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J130">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>38</v>
       </c>
@@ -2975,11 +3844,14 @@
       <c r="H131" t="str">
         <v>4.0.46</v>
       </c>
-      <c r="I131">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I131" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J131">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>5</v>
       </c>
@@ -2989,11 +3861,14 @@
       <c r="H132" t="str">
         <v>4.0.45</v>
       </c>
-      <c r="I132">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I132" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="J132">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>8</v>
       </c>
@@ -3003,11 +3878,14 @@
       <c r="H133" t="str">
         <v>4.0.44</v>
       </c>
-      <c r="I133">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I133" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J133">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>11</v>
       </c>
@@ -3017,11 +3895,14 @@
       <c r="H134" t="str">
         <v>4.0.43</v>
       </c>
-      <c r="I134">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I134" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J134">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>34</v>
       </c>
@@ -3031,11 +3912,14 @@
       <c r="H135" t="str">
         <v>4.0.42</v>
       </c>
-      <c r="I135">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I135" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J135">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>39</v>
       </c>
@@ -3051,11 +3935,17 @@
       <c r="H136" t="str">
         <v>4.0.41</v>
       </c>
-      <c r="I136">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I136" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J136">
+        <v>6.5</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>5</v>
       </c>
@@ -3065,11 +3955,14 @@
       <c r="H137" t="str">
         <v>4.0.40</v>
       </c>
-      <c r="I137">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I137" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J137">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>8</v>
       </c>
@@ -3079,11 +3972,14 @@
       <c r="H138" t="str">
         <v>4.0.39</v>
       </c>
-      <c r="I138">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I138" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J138">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
         <v>11</v>
       </c>
@@ -3093,11 +3989,14 @@
       <c r="H139" t="str">
         <v>4.0.38</v>
       </c>
-      <c r="I139">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I139" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J139">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>34</v>
       </c>
@@ -3107,11 +4006,14 @@
       <c r="H140" t="str">
         <v>4.0.37</v>
       </c>
-      <c r="I140">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J140">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>40</v>
       </c>
@@ -3127,11 +4029,14 @@
       <c r="H141" t="str">
         <v>4.0.36</v>
       </c>
-      <c r="I141">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I141" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J141">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>5</v>
       </c>
@@ -3141,11 +4046,14 @@
       <c r="H142" t="str">
         <v>4.0.35</v>
       </c>
-      <c r="I142">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I142" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J142">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>8</v>
       </c>
@@ -3155,11 +4063,14 @@
       <c r="H143" t="str">
         <v>4.0.34</v>
       </c>
-      <c r="I143">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I143" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="J143">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
         <v>11</v>
       </c>
@@ -3169,11 +4080,14 @@
       <c r="H144" t="str">
         <v>4.0.33</v>
       </c>
-      <c r="I144">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I144" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="J144">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>34</v>
       </c>
@@ -3183,11 +4097,14 @@
       <c r="H145" t="str">
         <v>4.0.32</v>
       </c>
-      <c r="I145">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J145">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>41</v>
       </c>
@@ -3203,11 +4120,14 @@
       <c r="H146" t="str">
         <v>4.0.31</v>
       </c>
-      <c r="I146">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I146" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J146">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
         <v>5</v>
       </c>
@@ -3217,11 +4137,14 @@
       <c r="H147" t="str">
         <v>4.0.30</v>
       </c>
-      <c r="I147">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I147" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J147">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>8</v>
       </c>
@@ -3231,11 +4154,14 @@
       <c r="H148" t="str">
         <v>4.0.29</v>
       </c>
-      <c r="I148">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I148" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J148">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
         <v>11</v>
       </c>
@@ -3245,11 +4171,14 @@
       <c r="H149" t="str">
         <v>4.0.28</v>
       </c>
-      <c r="I149">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I149" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J149">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
         <v>34</v>
       </c>
@@ -3259,11 +4188,14 @@
       <c r="H150" t="str">
         <v>4.0.27</v>
       </c>
-      <c r="I150">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I150" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J150">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>42</v>
       </c>
@@ -3279,11 +4211,14 @@
       <c r="H151" t="str">
         <v>4.0.26</v>
       </c>
-      <c r="I151">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I151" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="J151">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
         <v>43</v>
       </c>
@@ -3293,11 +4228,14 @@
       <c r="H152" t="str">
         <v>4.0.25</v>
       </c>
-      <c r="I152">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I152" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="J152">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
         <v>5</v>
       </c>
@@ -3307,11 +4245,14 @@
       <c r="H153" t="str">
         <v>4.0.24</v>
       </c>
-      <c r="I153">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I153" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J153">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
         <v>8</v>
       </c>
@@ -3321,11 +4262,14 @@
       <c r="H154" t="str">
         <v>4.0.23</v>
       </c>
-      <c r="I154">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I154" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J154">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
         <v>11</v>
       </c>
@@ -3335,11 +4279,14 @@
       <c r="H155" t="str">
         <v>4.0.22</v>
       </c>
-      <c r="I155">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I155" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J155">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
         <v>34</v>
       </c>
@@ -3349,11 +4296,14 @@
       <c r="H156" t="str">
         <v>4.0.21</v>
       </c>
-      <c r="I156">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I156" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J156">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -3369,11 +4319,14 @@
       <c r="H157" t="str">
         <v>4.0.20</v>
       </c>
-      <c r="I157">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I157" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="J157">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
         <v>43</v>
       </c>
@@ -3383,11 +4336,14 @@
       <c r="H158" t="str">
         <v>4.0.19</v>
       </c>
-      <c r="I158">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I158" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J158">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
         <v>5</v>
       </c>
@@ -3397,11 +4353,14 @@
       <c r="H159" t="str">
         <v>4.0.18</v>
       </c>
-      <c r="I159">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I159" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J159">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
         <v>8</v>
       </c>
@@ -3411,11 +4370,14 @@
       <c r="H160" t="str">
         <v>4.0.17</v>
       </c>
-      <c r="I160">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I160" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J160">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
         <v>11</v>
       </c>
@@ -3425,11 +4387,14 @@
       <c r="H161" t="str">
         <v>4.0.16</v>
       </c>
-      <c r="I161">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I161" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J161">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B162" t="s">
         <v>34</v>
       </c>
@@ -3439,11 +4404,14 @@
       <c r="H162" t="str">
         <v>4.0.15</v>
       </c>
-      <c r="I162">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I162" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J162">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>45</v>
       </c>
@@ -3459,11 +4427,14 @@
       <c r="H163" t="str">
         <v>4.0.14</v>
       </c>
-      <c r="I163">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I163" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J163">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
         <v>43</v>
       </c>
@@ -3473,11 +4444,14 @@
       <c r="H164" t="str">
         <v>4.0.13</v>
       </c>
-      <c r="I164">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I164" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="J164">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B165" t="s">
         <v>5</v>
       </c>
@@ -3487,11 +4461,14 @@
       <c r="H165" t="str">
         <v>4.0.12</v>
       </c>
-      <c r="I165">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I165" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="J165">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
         <v>8</v>
       </c>
@@ -3501,11 +4478,14 @@
       <c r="H166" t="str">
         <v>4.0.11</v>
       </c>
-      <c r="I166">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I166" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J166">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B167" t="s">
         <v>11</v>
       </c>
@@ -3515,11 +4495,14 @@
       <c r="H167" t="str">
         <v>4.0.10</v>
       </c>
-      <c r="I167">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I167" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="J167">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B168" t="s">
         <v>34</v>
       </c>
@@ -3529,11 +4512,14 @@
       <c r="H168" t="str">
         <v>4.0.9</v>
       </c>
-      <c r="I168">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I168" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J168">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>46</v>
       </c>
@@ -3549,11 +4535,14 @@
       <c r="H169" t="str">
         <v>4.0.8</v>
       </c>
-      <c r="I169">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I169" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="J169">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B170" t="s">
         <v>5</v>
       </c>
@@ -3563,11 +4552,14 @@
       <c r="H170" t="str">
         <v>4.0.7</v>
       </c>
-      <c r="I170">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I170" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J170">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
         <v>8</v>
       </c>
@@ -3577,11 +4569,14 @@
       <c r="H171" t="str">
         <v>4.0.6</v>
       </c>
-      <c r="I171">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I171" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J171">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B172" t="s">
         <v>11</v>
       </c>
@@ -3591,11 +4586,14 @@
       <c r="H172" t="str">
         <v>4.0.5</v>
       </c>
-      <c r="I172">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I172" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J172">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
         <v>34</v>
       </c>
@@ -3605,11 +4603,14 @@
       <c r="H173" t="str">
         <v>4.0.4</v>
       </c>
-      <c r="I173">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I173" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J173">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>47</v>
       </c>
@@ -3625,11 +4626,14 @@
       <c r="H174" t="str">
         <v>4.0.3</v>
       </c>
-      <c r="I174">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I174" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J174">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
         <v>5</v>
       </c>
@@ -3639,11 +4643,14 @@
       <c r="H175" t="str">
         <v>4.0.2</v>
       </c>
-      <c r="I175">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I175" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J175">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
         <v>8</v>
       </c>
@@ -3653,11 +4660,14 @@
       <c r="H176" t="str">
         <v>4.0.1</v>
       </c>
-      <c r="I176">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I176" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="J176">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>11</v>
       </c>
@@ -3667,11 +4677,14 @@
       <c r="H177" t="str">
         <v>4.0.0</v>
       </c>
-      <c r="I177">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I177" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J177">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>34</v>
       </c>
@@ -3679,7 +4692,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>48</v>
       </c>
@@ -3693,7 +4706,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>5</v>
       </c>
@@ -3701,7 +4714,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
         <v>8</v>
       </c>
@@ -3709,7 +4722,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>11</v>
       </c>
@@ -3717,7 +4730,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
         <v>34</v>
       </c>
@@ -3725,7 +4738,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>49</v>
       </c>
@@ -3739,7 +4752,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>5</v>
       </c>
@@ -3747,7 +4760,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>8</v>
       </c>
@@ -3755,7 +4768,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>11</v>
       </c>
@@ -3763,7 +4776,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>34</v>
       </c>
@@ -3771,7 +4784,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>50</v>
       </c>
@@ -3785,7 +4798,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>5</v>
       </c>
@@ -3793,7 +4806,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>8</v>
       </c>
@@ -3801,7 +4814,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>11</v>
       </c>
